--- a/backend/data/audit_report_templates/financial_statements/listed_consolidated.xlsx
+++ b/backend/data/audit_report_templates/financial_statements/listed_consolidated.xlsx
@@ -2646,7 +2646,7 @@
       <c r="E3" s="226" t="n"/>
       <c r="F3" s="227" t="inlineStr">
         <is>
-          <t>单位：人民币元</t>
+          <t>单位：{{currency_unit}}</t>
         </is>
       </c>
       <c r="G3" s="224" t="n"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B7" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{{note_ref:BS-002}}</t>
         </is>
       </c>
       <c r="C7" s="256" t="inlineStr">
@@ -2769,7 +2769,11 @@
           <t xml:space="preserve">  交易性金融资产</t>
         </is>
       </c>
-      <c r="B8" s="257" t="n"/>
+      <c r="B8" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-003}}</t>
+        </is>
+      </c>
       <c r="C8" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-003:current}}</t>
@@ -2797,7 +2801,11 @@
           <t xml:space="preserve">  衍生金融资产</t>
         </is>
       </c>
-      <c r="B9" s="257" t="n"/>
+      <c r="B9" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-004}}</t>
+        </is>
+      </c>
       <c r="C9" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-004:current}}</t>
@@ -2825,7 +2833,11 @@
           <t xml:space="preserve">  应收票据</t>
         </is>
       </c>
-      <c r="B10" s="257" t="n"/>
+      <c r="B10" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-005}};{{note_ref:BS-005:parent}}</t>
+        </is>
+      </c>
       <c r="C10" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-005:current}}</t>
@@ -2853,7 +2865,11 @@
           <t xml:space="preserve">  应收账款</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
+      <c r="B11" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-006}};{{note_ref:BS-006:parent}}</t>
+        </is>
+      </c>
       <c r="C11" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-006:current}}</t>
@@ -2881,7 +2897,11 @@
           <t xml:space="preserve">  应收款项融资</t>
         </is>
       </c>
-      <c r="B12" s="257" t="n"/>
+      <c r="B12" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-007}}</t>
+        </is>
+      </c>
       <c r="C12" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-007:current}}</t>
@@ -2909,7 +2929,11 @@
           <t xml:space="preserve">  预付款项</t>
         </is>
       </c>
-      <c r="B13" s="257" t="n"/>
+      <c r="B13" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-008}}</t>
+        </is>
+      </c>
       <c r="C13" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-008:current}}</t>
@@ -2937,7 +2961,11 @@
           <t xml:space="preserve">  其他应收款</t>
         </is>
       </c>
-      <c r="B14" s="257" t="n"/>
+      <c r="B14" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-009}};{{note_ref:BS-009:parent}}</t>
+        </is>
+      </c>
       <c r="C14" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-009:current}}</t>
@@ -3021,7 +3049,11 @@
           <t xml:space="preserve">  存货</t>
         </is>
       </c>
-      <c r="B17" s="257" t="n"/>
+      <c r="B17" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-012}}</t>
+        </is>
+      </c>
       <c r="C17" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-012:current}}</t>
@@ -3082,7 +3114,11 @@
           <t xml:space="preserve">  合同资产</t>
         </is>
       </c>
-      <c r="B19" s="257" t="n"/>
+      <c r="B19" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-014}}</t>
+        </is>
+      </c>
       <c r="C19" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-014:current}}</t>
@@ -3138,7 +3174,11 @@
           <t xml:space="preserve">  一年内到期的非流动资产</t>
         </is>
       </c>
-      <c r="B21" s="257" t="n"/>
+      <c r="B21" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-016}}</t>
+        </is>
+      </c>
       <c r="C21" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-016:current}}</t>
@@ -3166,7 +3206,11 @@
           <t xml:space="preserve">  其他流动资产</t>
         </is>
       </c>
-      <c r="B22" s="257" t="n"/>
+      <c r="B22" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-017}}</t>
+        </is>
+      </c>
       <c r="C22" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-017:current}}</t>
@@ -3230,7 +3274,11 @@
           <t xml:space="preserve">  债权投资</t>
         </is>
       </c>
-      <c r="B25" s="257" t="n"/>
+      <c r="B25" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-020}}</t>
+        </is>
+      </c>
       <c r="C25" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-020:current}}</t>
@@ -3258,7 +3306,11 @@
           <t xml:space="preserve">  其他债权投资</t>
         </is>
       </c>
-      <c r="B26" s="257" t="n"/>
+      <c r="B26" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-021}}</t>
+        </is>
+      </c>
       <c r="C26" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-021:current}}</t>
@@ -3302,7 +3354,11 @@
           <t xml:space="preserve">  长期应收款</t>
         </is>
       </c>
-      <c r="B27" s="257" t="n"/>
+      <c r="B27" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-022}}</t>
+        </is>
+      </c>
       <c r="C27" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-022:current}}</t>
@@ -3330,7 +3386,11 @@
           <t xml:space="preserve"> 设定受益计划净资产</t>
         </is>
       </c>
-      <c r="B28" s="257" t="n"/>
+      <c r="B28" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-023}}</t>
+        </is>
+      </c>
       <c r="C28" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-023:current}}</t>
@@ -3358,7 +3418,11 @@
           <t xml:space="preserve">  长期股权投资</t>
         </is>
       </c>
-      <c r="B29" s="257" t="n"/>
+      <c r="B29" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-024}};{{note_ref:BS-024:parent}}</t>
+        </is>
+      </c>
       <c r="C29" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-024:current}}</t>
@@ -3386,7 +3450,11 @@
           <t xml:space="preserve">  其他权益工具投资</t>
         </is>
       </c>
-      <c r="B30" s="257" t="n"/>
+      <c r="B30" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-025}}</t>
+        </is>
+      </c>
       <c r="C30" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-025:current}}</t>
@@ -3414,7 +3482,11 @@
           <t xml:space="preserve">  其他非流动金融资产</t>
         </is>
       </c>
-      <c r="B31" s="257" t="n"/>
+      <c r="B31" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-026}}</t>
+        </is>
+      </c>
       <c r="C31" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-026:current}}</t>
@@ -3442,7 +3514,11 @@
           <t xml:space="preserve">  投资性房地产</t>
         </is>
       </c>
-      <c r="B32" s="257" t="n"/>
+      <c r="B32" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-027}}</t>
+        </is>
+      </c>
       <c r="C32" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-027:current}}</t>
@@ -3470,7 +3546,11 @@
           <t xml:space="preserve">  固定资产</t>
         </is>
       </c>
-      <c r="B33" s="257" t="n"/>
+      <c r="B33" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-028}}</t>
+        </is>
+      </c>
       <c r="C33" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-028:current}}</t>
@@ -3514,7 +3594,11 @@
           <t xml:space="preserve">  在建工程</t>
         </is>
       </c>
-      <c r="B34" s="257" t="n"/>
+      <c r="B34" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-029}}</t>
+        </is>
+      </c>
       <c r="C34" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-029:current}}</t>
@@ -3542,7 +3626,11 @@
           <t xml:space="preserve">  生产性生物资产 </t>
         </is>
       </c>
-      <c r="B35" s="257" t="n"/>
+      <c r="B35" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-030}}</t>
+        </is>
+      </c>
       <c r="C35" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-030:current}}</t>
@@ -3598,7 +3686,11 @@
           <t xml:space="preserve"> 使用权资产</t>
         </is>
       </c>
-      <c r="B37" s="257" t="n"/>
+      <c r="B37" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-032}}</t>
+        </is>
+      </c>
       <c r="C37" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-032:current}}</t>
@@ -3626,7 +3718,11 @@
           <t xml:space="preserve">  无形资产</t>
         </is>
       </c>
-      <c r="B38" s="257" t="n"/>
+      <c r="B38" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-033}}</t>
+        </is>
+      </c>
       <c r="C38" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-033:current}}</t>
@@ -3687,7 +3783,11 @@
           <t xml:space="preserve">  开发支出</t>
         </is>
       </c>
-      <c r="B40" s="257" t="n"/>
+      <c r="B40" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-035}}</t>
+        </is>
+      </c>
       <c r="C40" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-035:current}}</t>
@@ -3748,7 +3848,11 @@
           <t xml:space="preserve">  商誉</t>
         </is>
       </c>
-      <c r="B42" s="257" t="n"/>
+      <c r="B42" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-037}}</t>
+        </is>
+      </c>
       <c r="C42" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-037:current}}</t>
@@ -3776,7 +3880,11 @@
           <t xml:space="preserve">  长期待摊费用</t>
         </is>
       </c>
-      <c r="B43" s="257" t="n"/>
+      <c r="B43" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-038}}</t>
+        </is>
+      </c>
       <c r="C43" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-038:current}}</t>
@@ -3832,7 +3940,11 @@
           <t xml:space="preserve">  其他非流动资产</t>
         </is>
       </c>
-      <c r="B45" s="257" t="n"/>
+      <c r="B45" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-040}}</t>
+        </is>
+      </c>
       <c r="C45" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-040:current}}</t>
@@ -4076,7 +4188,7 @@
       </c>
       <c r="B7" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">　</t>
+          <t>{{note_ref:BS-044}}</t>
         </is>
       </c>
       <c r="C7" s="256" t="inlineStr">
@@ -4106,7 +4218,11 @@
           <t xml:space="preserve">  交易性金融负债</t>
         </is>
       </c>
-      <c r="B8" s="257" t="n"/>
+      <c r="B8" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-045}}</t>
+        </is>
+      </c>
       <c r="C8" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-045:current}}</t>
@@ -4134,7 +4250,11 @@
           <t xml:space="preserve"> 衍生金融负债</t>
         </is>
       </c>
-      <c r="B9" s="257" t="n"/>
+      <c r="B9" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-046}}</t>
+        </is>
+      </c>
       <c r="C9" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-046:current}}</t>
@@ -4162,7 +4282,11 @@
           <t xml:space="preserve">  应付票据</t>
         </is>
       </c>
-      <c r="B10" s="257" t="n"/>
+      <c r="B10" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-047}}</t>
+        </is>
+      </c>
       <c r="C10" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-047:current}}</t>
@@ -4190,7 +4314,11 @@
           <t xml:space="preserve">  应付账款</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
+      <c r="B11" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-048}}</t>
+        </is>
+      </c>
       <c r="C11" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-048:current}}</t>
@@ -4218,7 +4346,11 @@
           <t xml:space="preserve">  预收款项</t>
         </is>
       </c>
-      <c r="B12" s="257" t="n"/>
+      <c r="B12" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-049}}</t>
+        </is>
+      </c>
       <c r="C12" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-049:current}}</t>
@@ -4246,7 +4378,11 @@
           <t xml:space="preserve">  合同负债</t>
         </is>
       </c>
-      <c r="B13" s="257" t="n"/>
+      <c r="B13" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-050}}</t>
+        </is>
+      </c>
       <c r="C13" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-050:current}}</t>
@@ -4274,7 +4410,11 @@
           <t xml:space="preserve">  应付职工薪酬</t>
         </is>
       </c>
-      <c r="B14" s="257" t="n"/>
+      <c r="B14" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-051}}</t>
+        </is>
+      </c>
       <c r="C14" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-051:current}}</t>
@@ -4302,7 +4442,11 @@
           <t xml:space="preserve">  应交税费</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
+      <c r="B15" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-052}}</t>
+        </is>
+      </c>
       <c r="C15" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-052:current}}</t>
@@ -4330,7 +4474,11 @@
           <t xml:space="preserve">  其他应付款</t>
         </is>
       </c>
-      <c r="B16" s="257" t="n"/>
+      <c r="B16" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-053}}</t>
+        </is>
+      </c>
       <c r="C16" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-053:current}}</t>
@@ -4442,7 +4590,11 @@
           <t xml:space="preserve">  一年内到期的非流动负债</t>
         </is>
       </c>
-      <c r="B20" s="257" t="n"/>
+      <c r="B20" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-057}}</t>
+        </is>
+      </c>
       <c r="C20" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-057:current}}</t>
@@ -4470,7 +4622,11 @@
           <t xml:space="preserve">  其他流动负债</t>
         </is>
       </c>
-      <c r="B21" s="257" t="n"/>
+      <c r="B21" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-058}}</t>
+        </is>
+      </c>
       <c r="C21" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-058:current}}</t>
@@ -4539,7 +4695,11 @@
           <t xml:space="preserve">  长期借款</t>
         </is>
       </c>
-      <c r="B24" s="257" t="n"/>
+      <c r="B24" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-061}}</t>
+        </is>
+      </c>
       <c r="C24" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-061:current}}</t>
@@ -4567,7 +4727,11 @@
           <t xml:space="preserve">  应付债券</t>
         </is>
       </c>
-      <c r="B25" s="257" t="n"/>
+      <c r="B25" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-062}}</t>
+        </is>
+      </c>
       <c r="C25" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-062:current}}</t>
@@ -4651,7 +4815,11 @@
           <t xml:space="preserve"> 租赁负债</t>
         </is>
       </c>
-      <c r="B28" s="257" t="n"/>
+      <c r="B28" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-065}}</t>
+        </is>
+      </c>
       <c r="C28" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-065:current}}</t>
@@ -4679,7 +4847,11 @@
           <t xml:space="preserve">  长期应付款</t>
         </is>
       </c>
-      <c r="B29" s="257" t="n"/>
+      <c r="B29" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-066}}</t>
+        </is>
+      </c>
       <c r="C29" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-066:current}}</t>
@@ -4707,7 +4879,11 @@
           <t xml:space="preserve"> 长期应付职工薪酬</t>
         </is>
       </c>
-      <c r="B30" s="257" t="n"/>
+      <c r="B30" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-067}}</t>
+        </is>
+      </c>
       <c r="C30" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-067:current}}</t>
@@ -4735,7 +4911,11 @@
           <t xml:space="preserve">  预计负债</t>
         </is>
       </c>
-      <c r="B31" s="257" t="n"/>
+      <c r="B31" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-068}}</t>
+        </is>
+      </c>
       <c r="C31" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-068:current}}</t>
@@ -4768,7 +4948,11 @@
           <t xml:space="preserve">  递延收益</t>
         </is>
       </c>
-      <c r="B32" s="257" t="n"/>
+      <c r="B32" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-069}}</t>
+        </is>
+      </c>
       <c r="C32" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-069:current}}</t>
@@ -4824,7 +5008,11 @@
           <t xml:space="preserve">  其他非流动负债</t>
         </is>
       </c>
-      <c r="B34" s="257" t="n"/>
+      <c r="B34" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-071}}</t>
+        </is>
+      </c>
       <c r="C34" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-071:current}}</t>
@@ -4920,7 +5108,11 @@
           <t xml:space="preserve">  股本</t>
         </is>
       </c>
-      <c r="B39" s="257" t="n"/>
+      <c r="B39" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-075}}</t>
+        </is>
+      </c>
       <c r="C39" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-075:current}}</t>
@@ -4948,7 +5140,11 @@
           <t xml:space="preserve"> 其他权益工具</t>
         </is>
       </c>
-      <c r="B40" s="257" t="n"/>
+      <c r="B40" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-076}}</t>
+        </is>
+      </c>
       <c r="C40" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-076:current}}</t>
@@ -5035,7 +5231,11 @@
           <t xml:space="preserve">  资本公积</t>
         </is>
       </c>
-      <c r="B43" s="257" t="n"/>
+      <c r="B43" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-079}}</t>
+        </is>
+      </c>
       <c r="C43" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-079:current}}</t>
@@ -5093,7 +5293,11 @@
           <t xml:space="preserve"> 其他综合收益</t>
         </is>
       </c>
-      <c r="B45" s="257" t="n"/>
+      <c r="B45" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-081}}</t>
+        </is>
+      </c>
       <c r="C45" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-081:current}}</t>
@@ -5122,7 +5326,11 @@
           <t xml:space="preserve">  专项储备</t>
         </is>
       </c>
-      <c r="B46" s="257" t="n"/>
+      <c r="B46" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-082}}</t>
+        </is>
+      </c>
       <c r="C46" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-082:current}}</t>
@@ -5151,7 +5359,11 @@
           <t xml:space="preserve">  盈余公积</t>
         </is>
       </c>
-      <c r="B47" s="257" t="n"/>
+      <c r="B47" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-083}}</t>
+        </is>
+      </c>
       <c r="C47" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-083:current}}</t>
@@ -5180,7 +5392,11 @@
           <t xml:space="preserve">  未分配利润</t>
         </is>
       </c>
-      <c r="B48" s="257" t="n"/>
+      <c r="B48" s="257" t="inlineStr">
+        <is>
+          <t>{{note_ref:BS-084}}</t>
+        </is>
+      </c>
       <c r="C48" s="256" t="inlineStr">
         <is>
           <t>{{row:BS-084:current}}</t>
@@ -5332,10 +5548,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
     <row r="59">
       <c r="C59" s="262">
         <f>资产负债表!C53-资产负债表续!C58</f>
@@ -5426,7 +5638,7 @@
       <c r="E3" s="151" t="n"/>
       <c r="F3" s="152" t="inlineStr">
         <is>
-          <t xml:space="preserve">          单位：人民币元</t>
+          <t xml:space="preserve">          单位：{{currency_unit}}</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5754,11 @@
           <t xml:space="preserve">             税金及附加</t>
         </is>
       </c>
-      <c r="B8" s="164" t="n"/>
+      <c r="B8" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-003}}</t>
+        </is>
+      </c>
       <c r="C8" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-003:current}}</t>
@@ -5575,7 +5791,11 @@
           <t xml:space="preserve">             销售费用</t>
         </is>
       </c>
-      <c r="B9" s="164" t="n"/>
+      <c r="B9" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-004}}</t>
+        </is>
+      </c>
       <c r="C9" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-004:current}}</t>
@@ -5603,7 +5823,11 @@
           <t xml:space="preserve">             管理费用</t>
         </is>
       </c>
-      <c r="B10" s="164" t="n"/>
+      <c r="B10" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-005}}</t>
+        </is>
+      </c>
       <c r="C10" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-005:current}}</t>
@@ -5631,7 +5855,11 @@
           <t xml:space="preserve">             研发费用</t>
         </is>
       </c>
-      <c r="B11" s="164" t="n"/>
+      <c r="B11" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-006}}</t>
+        </is>
+      </c>
       <c r="C11" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-006:current}}</t>
@@ -5659,7 +5887,11 @@
           <t xml:space="preserve">             财务费用</t>
         </is>
       </c>
-      <c r="B12" s="164" t="n"/>
+      <c r="B12" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-007}}</t>
+        </is>
+      </c>
       <c r="C12" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-007:current}}</t>
@@ -5776,7 +6008,11 @@
           <t xml:space="preserve">            投资收益(损失以“-”号填列）</t>
         </is>
       </c>
-      <c r="B16" s="164" t="n"/>
+      <c r="B16" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-011}};{{note_ref:IS-011:parent}}</t>
+        </is>
+      </c>
       <c r="C16" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-011:current}}</t>
@@ -5860,7 +6096,11 @@
           <t xml:space="preserve">            净敞口套期收益(损失以“-”号填列）</t>
         </is>
       </c>
-      <c r="B19" s="164" t="n"/>
+      <c r="B19" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-014}}</t>
+        </is>
+      </c>
       <c r="C19" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-014:current}}</t>
@@ -5888,7 +6128,11 @@
           <t xml:space="preserve">            公允价值变动收益(损失以“-”号填列）</t>
         </is>
       </c>
-      <c r="B20" s="164" t="n"/>
+      <c r="B20" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-015}}</t>
+        </is>
+      </c>
       <c r="C20" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-015:current}}</t>
@@ -5916,7 +6160,11 @@
           <t xml:space="preserve">            信用减值损失(损失以“-”号填列）</t>
         </is>
       </c>
-      <c r="B21" s="164" t="n"/>
+      <c r="B21" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-016}}</t>
+        </is>
+      </c>
       <c r="C21" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-016:current}}</t>
@@ -5946,7 +6194,11 @@
           <t xml:space="preserve">            资产减值损失(损失以“-”号填列）</t>
         </is>
       </c>
-      <c r="B22" s="164" t="n"/>
+      <c r="B22" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-017}}</t>
+        </is>
+      </c>
       <c r="C22" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-017:current}}</t>
@@ -5976,7 +6228,11 @@
           <t xml:space="preserve">            资产处置收益(损失以“-”号填列）</t>
         </is>
       </c>
-      <c r="B23" s="164" t="n"/>
+      <c r="B23" s="164" t="inlineStr">
+        <is>
+          <t>{{note_ref:IS-018}}</t>
+        </is>
+      </c>
       <c r="C23" s="256" t="inlineStr">
         <is>
           <t>{{row:IS-018:current}}</t>
@@ -7176,7 +7432,7 @@
       </c>
       <c r="E3" s="100" t="inlineStr">
         <is>
-          <t>单位：人民币元</t>
+          <t>单位：{{currency_unit}}</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8585,6 @@
       <c r="B48" s="136" t="n"/>
       <c r="E48" s="137" t="n"/>
     </row>
-    <row r="49"/>
     <row r="50" ht="65.25" customHeight="1">
       <c r="A50" s="138" t="inlineStr">
         <is>
@@ -8423,7 +8678,7 @@
       <c r="E2" s="7" t="n"/>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>2025年度</t>
+          <t>{{audit_year}}年度</t>
         </is>
       </c>
       <c r="I2" s="7" t="n"/>
@@ -8450,13 +8705,13 @@
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="60" t="inlineStr">
         <is>
-          <t>编制单位：XXXX股份有限公司</t>
+          <t>编制单位：{{company_full_name}}</t>
         </is>
       </c>
       <c r="J3" s="9" t="n"/>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>单位：人民币元</t>
+          <t>单位：{{currency_unit}}</t>
         </is>
       </c>
       <c r="W3" s="9" t="n"/>
@@ -8780,18 +9035,58 @@
         <f>B8+C8+D8+E8+F8-G8+H8+I8+J8+K8+L8+M8</f>
         <v/>
       </c>
-      <c r="O8" s="319" t="n"/>
-      <c r="P8" s="320" t="n"/>
+      <c r="O8" s="319" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P8" s="320" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q8" s="320" t="n"/>
       <c r="R8" s="320" t="n"/>
-      <c r="S8" s="318" t="n"/>
-      <c r="T8" s="318" t="n"/>
-      <c r="U8" s="320" t="n"/>
-      <c r="V8" s="317" t="n"/>
-      <c r="W8" s="317" t="n"/>
-      <c r="X8" s="317" t="n"/>
-      <c r="Y8" s="321" t="n"/>
-      <c r="Z8" s="318" t="n"/>
+      <c r="S8" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T8" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U8" s="320" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V8" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W8" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X8" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y8" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z8" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA8" s="318">
         <f>O8+P8+Q8+R8+S8-T8+V8+W8+X8+Y8+Z8+U8</f>
         <v/>
@@ -8803,34 +9098,114 @@
           <t xml:space="preserve">  加：会计政策变更</t>
         </is>
       </c>
-      <c r="B9" s="322" t="n"/>
-      <c r="C9" s="322" t="n"/>
+      <c r="B9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D9" s="322" t="n"/>
       <c r="E9" s="322" t="n"/>
-      <c r="F9" s="322" t="n"/>
-      <c r="G9" s="322" t="n"/>
-      <c r="H9" s="322" t="n"/>
-      <c r="I9" s="323" t="n"/>
-      <c r="J9" s="322" t="n"/>
-      <c r="K9" s="322" t="n"/>
-      <c r="L9" s="322" t="n"/>
-      <c r="M9" s="322" t="n"/>
+      <c r="F9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I9" s="323" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N9" s="318">
         <f>B9+C9+D9+E9+F9-G9+H9+I9+J9+K9+L9+M9</f>
         <v/>
       </c>
-      <c r="O9" s="324" t="n"/>
-      <c r="P9" s="317" t="n"/>
+      <c r="O9" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q9" s="317" t="n"/>
       <c r="R9" s="317" t="n"/>
-      <c r="S9" s="318" t="n"/>
-      <c r="T9" s="318" t="n"/>
-      <c r="U9" s="317" t="n"/>
-      <c r="V9" s="317" t="n"/>
-      <c r="W9" s="317" t="n"/>
-      <c r="X9" s="317" t="n"/>
-      <c r="Y9" s="321" t="n"/>
-      <c r="Z9" s="318" t="n"/>
+      <c r="S9" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T9" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y9" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z9" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA9" s="318">
         <f>O9+P9+Q9+R9+S9-T9+V9+W9+X9+Y9+Z9+U9</f>
         <v/>
@@ -8842,34 +9217,114 @@
           <t xml:space="preserve">           前期差错更正</t>
         </is>
       </c>
-      <c r="B10" s="322" t="n"/>
-      <c r="C10" s="322" t="n"/>
+      <c r="B10" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C10" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D10" s="322" t="n"/>
       <c r="E10" s="322" t="n"/>
-      <c r="F10" s="322" t="n"/>
-      <c r="G10" s="322" t="n"/>
-      <c r="H10" s="322" t="n"/>
-      <c r="I10" s="323" t="n"/>
-      <c r="J10" s="322" t="n"/>
-      <c r="K10" s="322" t="n"/>
-      <c r="L10" s="322" t="n"/>
-      <c r="M10" s="322" t="n"/>
+      <c r="F10" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G10" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H10" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I10" s="323" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J10" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K10" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L10" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M10" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N10" s="318">
         <f>B10+C10+D10+E10+F10-G10+H10+I10+J10+K10+L10+M10</f>
         <v/>
       </c>
-      <c r="O10" s="324" t="n"/>
-      <c r="P10" s="317" t="n"/>
+      <c r="O10" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q10" s="317" t="n"/>
       <c r="R10" s="317" t="n"/>
-      <c r="S10" s="318" t="n"/>
-      <c r="T10" s="318" t="n"/>
-      <c r="U10" s="317" t="n"/>
-      <c r="V10" s="317" t="n"/>
-      <c r="W10" s="317" t="n"/>
-      <c r="X10" s="317" t="n"/>
-      <c r="Y10" s="321" t="n"/>
-      <c r="Z10" s="318" t="n"/>
+      <c r="S10" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T10" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y10" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z10" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA10" s="318">
         <f>O10+P10+Q10+R10+S10-T10+V10+W10+X10+Y10+Z10+U10</f>
         <v/>
@@ -8881,34 +9336,114 @@
           <t xml:space="preserve">           同一控制下企业合并</t>
         </is>
       </c>
-      <c r="B11" s="322" t="n"/>
-      <c r="C11" s="323" t="n"/>
+      <c r="B11" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C11" s="323" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D11" s="323" t="n"/>
       <c r="E11" s="323" t="n"/>
-      <c r="F11" s="323" t="n"/>
-      <c r="G11" s="322" t="n"/>
-      <c r="H11" s="322" t="n"/>
-      <c r="I11" s="325" t="n"/>
-      <c r="J11" s="322" t="n"/>
-      <c r="K11" s="322" t="n"/>
-      <c r="L11" s="322" t="n"/>
-      <c r="M11" s="322" t="n"/>
+      <c r="F11" s="323" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G11" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H11" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I11" s="325" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J11" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K11" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L11" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M11" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N11" s="318">
         <f>B11+C11+D11+E11+F11-G11+H11+I11+J11+K11+L11+M11</f>
         <v/>
       </c>
-      <c r="O11" s="324" t="n"/>
-      <c r="P11" s="317" t="n"/>
+      <c r="O11" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P11" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q11" s="317" t="n"/>
       <c r="R11" s="317" t="n"/>
-      <c r="S11" s="318" t="n"/>
-      <c r="T11" s="318" t="n"/>
-      <c r="U11" s="317" t="n"/>
-      <c r="V11" s="317" t="n"/>
-      <c r="W11" s="317" t="n"/>
-      <c r="X11" s="317" t="n"/>
-      <c r="Y11" s="321" t="n"/>
-      <c r="Z11" s="318" t="n"/>
+      <c r="S11" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T11" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U11" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V11" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W11" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X11" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y11" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z11" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-004:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA11" s="318">
         <f>O11+P11+Q11+R11+S11-T11+V11+W11+X11+Y11+Z11+U11</f>
         <v/>
@@ -8920,34 +9455,114 @@
           <t xml:space="preserve">           其他</t>
         </is>
       </c>
-      <c r="B12" s="317" t="n"/>
-      <c r="C12" s="324" t="n"/>
+      <c r="B12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C12" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D12" s="324" t="n"/>
       <c r="E12" s="324" t="n"/>
-      <c r="F12" s="324" t="n"/>
-      <c r="G12" s="317" t="n"/>
-      <c r="H12" s="317" t="n"/>
-      <c r="I12" s="321" t="n"/>
-      <c r="J12" s="317" t="n"/>
-      <c r="K12" s="317" t="n"/>
-      <c r="L12" s="317" t="n"/>
-      <c r="M12" s="317" t="n"/>
+      <c r="F12" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I12" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N12" s="318">
         <f>B12+C12+D12+E12+F12-G12+H12+I12+J12+K12+L12+M12</f>
         <v/>
       </c>
-      <c r="O12" s="324" t="n"/>
-      <c r="P12" s="317" t="n"/>
+      <c r="O12" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q12" s="317" t="n"/>
       <c r="R12" s="317" t="n"/>
-      <c r="S12" s="318" t="n"/>
-      <c r="T12" s="318" t="n"/>
-      <c r="U12" s="317" t="n"/>
-      <c r="V12" s="317" t="n"/>
-      <c r="W12" s="317" t="n"/>
-      <c r="X12" s="317" t="n"/>
-      <c r="Y12" s="321" t="n"/>
-      <c r="Z12" s="318" t="n"/>
+      <c r="S12" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T12" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X12" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y12" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z12" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA12" s="318">
         <f>O12+P12+Q12+R12+S12-T12+V12+W12+X12+Y12+Z12+U12</f>
         <v/>
@@ -9181,34 +9796,114 @@
           <t>（一）综合收益总额</t>
         </is>
       </c>
-      <c r="B15" s="317" t="n"/>
-      <c r="C15" s="317" t="n"/>
+      <c r="B15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D15" s="317" t="n"/>
       <c r="E15" s="317" t="n"/>
-      <c r="F15" s="317" t="n"/>
-      <c r="G15" s="317" t="n"/>
-      <c r="H15" s="317" t="n"/>
-      <c r="I15" s="324" t="n"/>
-      <c r="J15" s="317" t="n"/>
-      <c r="K15" s="317" t="n"/>
-      <c r="L15" s="317" t="n"/>
-      <c r="M15" s="317" t="n"/>
+      <c r="F15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N15" s="318">
         <f>B15+C15+D15+E15+F15-G15+H15+I15+J15+K15+L15+M15</f>
         <v/>
       </c>
-      <c r="O15" s="324" t="n"/>
-      <c r="P15" s="324" t="n"/>
+      <c r="O15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q15" s="324" t="n"/>
       <c r="R15" s="324" t="n"/>
-      <c r="S15" s="317" t="n"/>
-      <c r="T15" s="318" t="n"/>
-      <c r="U15" s="317" t="n"/>
-      <c r="V15" s="317" t="n"/>
-      <c r="W15" s="324" t="n"/>
-      <c r="X15" s="317" t="n"/>
-      <c r="Y15" s="317" t="n"/>
-      <c r="Z15" s="317" t="n"/>
+      <c r="S15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T15" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA15" s="318">
         <f>O15+P15+Q15+R15+S15-T15+V15+W15+X15+Y15+Z15+U15</f>
         <v/>
@@ -9331,34 +10026,114 @@
           <t xml:space="preserve"> 1．股东投入的普通股</t>
         </is>
       </c>
-      <c r="B17" s="317" t="n"/>
-      <c r="C17" s="324" t="n"/>
+      <c r="B17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D17" s="324" t="n"/>
       <c r="E17" s="324" t="n"/>
-      <c r="F17" s="324" t="n"/>
-      <c r="G17" s="317" t="n"/>
-      <c r="H17" s="317" t="n"/>
-      <c r="I17" s="321" t="n"/>
-      <c r="J17" s="317" t="n"/>
-      <c r="K17" s="317" t="n"/>
-      <c r="L17" s="317" t="n"/>
-      <c r="M17" s="317" t="n"/>
+      <c r="F17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I17" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N17" s="318">
         <f>B17+C17+D17+E17+F17-G17+H17+I17+J17+K17+L17+M17</f>
         <v/>
       </c>
-      <c r="O17" s="324" t="n"/>
-      <c r="P17" s="324" t="n"/>
+      <c r="O17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q17" s="324" t="n"/>
       <c r="R17" s="324" t="n"/>
-      <c r="S17" s="324" t="n"/>
-      <c r="T17" s="321" t="n"/>
-      <c r="U17" s="317" t="n"/>
-      <c r="V17" s="317" t="n"/>
-      <c r="W17" s="324" t="n"/>
-      <c r="X17" s="317" t="n"/>
-      <c r="Y17" s="317" t="n"/>
-      <c r="Z17" s="317" t="n"/>
+      <c r="S17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T17" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA17" s="318">
         <f>O17+P17+Q17+R17+S17-T17+V17+W17+X17+Y17+Z17+U17</f>
         <v/>
@@ -9370,34 +10145,114 @@
           <t xml:space="preserve"> 2.  其他权益工具持有者投入资本</t>
         </is>
       </c>
-      <c r="B18" s="317" t="n"/>
-      <c r="C18" s="324" t="n"/>
+      <c r="B18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D18" s="324" t="n"/>
       <c r="E18" s="324" t="n"/>
-      <c r="F18" s="324" t="n"/>
-      <c r="G18" s="317" t="n"/>
-      <c r="H18" s="317" t="n"/>
-      <c r="I18" s="321" t="n"/>
-      <c r="J18" s="317" t="n"/>
-      <c r="K18" s="317" t="n"/>
-      <c r="L18" s="317" t="n"/>
-      <c r="M18" s="317" t="n"/>
+      <c r="F18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I18" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N18" s="318">
         <f>B18+C18+D18+E18+F18-G18+H18+I18+J18+K18+L18+M18</f>
         <v/>
       </c>
-      <c r="O18" s="324" t="n"/>
-      <c r="P18" s="324" t="n"/>
+      <c r="O18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q18" s="324" t="n"/>
       <c r="R18" s="324" t="n"/>
-      <c r="S18" s="324" t="n"/>
-      <c r="T18" s="321" t="n"/>
-      <c r="U18" s="317" t="n"/>
-      <c r="V18" s="317" t="n"/>
-      <c r="W18" s="324" t="n"/>
-      <c r="X18" s="317" t="n"/>
-      <c r="Y18" s="317" t="n"/>
-      <c r="Z18" s="317" t="n"/>
+      <c r="S18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T18" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA18" s="318">
         <f>O18+P18+Q18+R18+S18-T18+V18+W18+X18+Y18+Z18+U18</f>
         <v/>
@@ -9409,34 +10264,114 @@
           <t xml:space="preserve"> 3．股份支付计入股东权益的金额</t>
         </is>
       </c>
-      <c r="B19" s="317" t="n"/>
-      <c r="C19" s="324" t="n"/>
+      <c r="B19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C19" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D19" s="324" t="n"/>
       <c r="E19" s="324" t="n"/>
-      <c r="F19" s="324" t="n"/>
-      <c r="G19" s="317" t="n"/>
-      <c r="H19" s="317" t="n"/>
-      <c r="I19" s="321" t="n"/>
-      <c r="J19" s="317" t="n"/>
-      <c r="K19" s="317" t="n"/>
-      <c r="L19" s="317" t="n"/>
-      <c r="M19" s="317" t="n"/>
+      <c r="F19" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I19" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N19" s="318">
         <f>B19+C19+D19+E19+F19-G19+H19+I19+J19+K19+L19+M19</f>
         <v/>
       </c>
-      <c r="O19" s="324" t="n"/>
-      <c r="P19" s="324" t="n"/>
+      <c r="O19" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P19" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q19" s="324" t="n"/>
       <c r="R19" s="324" t="n"/>
-      <c r="S19" s="324" t="n"/>
-      <c r="T19" s="321" t="n"/>
-      <c r="U19" s="317" t="n"/>
-      <c r="V19" s="317" t="n"/>
-      <c r="W19" s="324" t="n"/>
-      <c r="X19" s="317" t="n"/>
-      <c r="Y19" s="317" t="n"/>
-      <c r="Z19" s="317" t="n"/>
+      <c r="S19" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T19" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W19" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z19" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA19" s="318">
         <f>O19+P19+Q19+R19+S19-T19+V19+W19+X19+Y19+Z19+U19</f>
         <v/>
@@ -9448,34 +10383,114 @@
           <t xml:space="preserve"> 4．其他</t>
         </is>
       </c>
-      <c r="B20" s="317" t="n"/>
-      <c r="C20" s="324" t="n"/>
+      <c r="B20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D20" s="324" t="n"/>
       <c r="E20" s="324" t="n"/>
-      <c r="F20" s="324" t="n"/>
-      <c r="G20" s="317" t="n"/>
-      <c r="H20" s="317" t="n"/>
-      <c r="I20" s="321" t="n"/>
-      <c r="J20" s="317" t="n"/>
-      <c r="K20" s="317" t="n"/>
-      <c r="L20" s="317" t="n"/>
-      <c r="M20" s="317" t="n"/>
+      <c r="F20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I20" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N20" s="318">
         <f>B20+C20+D20+E20+F20-G20+H20+I20+J20+K20+L20+M20</f>
         <v/>
       </c>
-      <c r="O20" s="324" t="n"/>
-      <c r="P20" s="324" t="n"/>
+      <c r="O20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q20" s="324" t="n"/>
       <c r="R20" s="324" t="n"/>
-      <c r="S20" s="324" t="n"/>
-      <c r="T20" s="321" t="n"/>
-      <c r="U20" s="317" t="n"/>
-      <c r="V20" s="317" t="n"/>
-      <c r="W20" s="324" t="n"/>
-      <c r="X20" s="317" t="n"/>
-      <c r="Y20" s="317" t="n"/>
-      <c r="Z20" s="317" t="n"/>
+      <c r="S20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T20" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA20" s="318">
         <f>O20+P20+Q20+R20+S20-T20+V20+W20+X20+Y20+Z20+U20</f>
         <v/>
@@ -9598,34 +10613,114 @@
           <t xml:space="preserve"> 1．提取盈余公积</t>
         </is>
       </c>
-      <c r="B22" s="317" t="n"/>
-      <c r="C22" s="324" t="n"/>
+      <c r="B22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D22" s="324" t="n"/>
       <c r="E22" s="324" t="n"/>
-      <c r="F22" s="324" t="n"/>
-      <c r="G22" s="317" t="n"/>
-      <c r="H22" s="317" t="n"/>
-      <c r="I22" s="321" t="n"/>
-      <c r="J22" s="317" t="n"/>
-      <c r="K22" s="317" t="n"/>
-      <c r="L22" s="317" t="n"/>
-      <c r="M22" s="317" t="n"/>
+      <c r="F22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I22" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N22" s="318">
         <f>B22+C22+D22+E22+F22-G22+H22+I22+J22+K22+L22+M22</f>
         <v/>
       </c>
-      <c r="O22" s="324" t="n"/>
-      <c r="P22" s="324" t="n"/>
+      <c r="O22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q22" s="324" t="n"/>
       <c r="R22" s="324" t="n"/>
-      <c r="S22" s="324" t="n"/>
-      <c r="T22" s="321" t="n"/>
-      <c r="U22" s="317" t="n"/>
-      <c r="V22" s="317" t="n"/>
-      <c r="W22" s="324" t="n"/>
-      <c r="X22" s="317" t="n"/>
-      <c r="Y22" s="317" t="n"/>
-      <c r="Z22" s="317" t="n"/>
+      <c r="S22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T22" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA22" s="318">
         <f>O22+P22+Q22+R22+S22-T22+V22+W22+X22+Y22+Z22+U22</f>
         <v/>
@@ -9637,32 +10732,120 @@
           <t xml:space="preserve"> 2．提取一般风险准备</t>
         </is>
       </c>
-      <c r="B23" s="317" t="n"/>
-      <c r="C23" s="324" t="n"/>
+      <c r="B23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D23" s="324" t="n"/>
       <c r="E23" s="324" t="n"/>
-      <c r="F23" s="324" t="n"/>
-      <c r="G23" s="317" t="n"/>
-      <c r="H23" s="317" t="n"/>
-      <c r="I23" s="321" t="n"/>
-      <c r="J23" s="317" t="n"/>
-      <c r="K23" s="317" t="n"/>
-      <c r="L23" s="317" t="n"/>
-      <c r="M23" s="317" t="n"/>
-      <c r="N23" s="318" t="n"/>
-      <c r="O23" s="324" t="n"/>
-      <c r="P23" s="324" t="n"/>
+      <c r="F23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I23" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:minority_interest}}</t>
+        </is>
+      </c>
+      <c r="N23" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:total_equity}}</t>
+        </is>
+      </c>
+      <c r="O23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q23" s="324" t="n"/>
       <c r="R23" s="324" t="n"/>
-      <c r="S23" s="324" t="n"/>
-      <c r="T23" s="321" t="n"/>
-      <c r="U23" s="317" t="n"/>
-      <c r="V23" s="317" t="n"/>
-      <c r="W23" s="324" t="n"/>
-      <c r="X23" s="317" t="n"/>
-      <c r="Y23" s="317" t="n"/>
-      <c r="Z23" s="317" t="n"/>
-      <c r="AA23" s="318" t="n"/>
+      <c r="S23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T23" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:minority_interest}}</t>
+        </is>
+      </c>
+      <c r="AA23" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:total_equity}}</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customFormat="1" customHeight="1" s="58">
       <c r="A24" s="42" t="inlineStr">
@@ -9670,34 +10853,114 @@
           <t xml:space="preserve"> 3．对股东（或所有者）的分配</t>
         </is>
       </c>
-      <c r="B24" s="317" t="n"/>
-      <c r="C24" s="324" t="n"/>
+      <c r="B24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C24" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D24" s="324" t="n"/>
       <c r="E24" s="324" t="n"/>
-      <c r="F24" s="324" t="n"/>
-      <c r="G24" s="317" t="n"/>
-      <c r="H24" s="317" t="n"/>
-      <c r="I24" s="321" t="n"/>
-      <c r="J24" s="317" t="n"/>
-      <c r="K24" s="317" t="n"/>
-      <c r="L24" s="317" t="n"/>
-      <c r="M24" s="317" t="n"/>
+      <c r="F24" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I24" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N24" s="318">
         <f>B24+C24+D24+E24+F24-G24+H24+I24+J24+K24+L24+M24</f>
         <v/>
       </c>
-      <c r="O24" s="324" t="n"/>
-      <c r="P24" s="324" t="n"/>
+      <c r="O24" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P24" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q24" s="324" t="n"/>
       <c r="R24" s="324" t="n"/>
-      <c r="S24" s="324" t="n"/>
-      <c r="T24" s="321" t="n"/>
-      <c r="U24" s="317" t="n"/>
-      <c r="V24" s="317" t="n"/>
-      <c r="W24" s="324" t="n"/>
-      <c r="X24" s="317" t="n"/>
-      <c r="Y24" s="317" t="n"/>
-      <c r="Z24" s="317" t="n"/>
+      <c r="S24" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T24" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W24" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z24" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA24" s="318">
         <f>O24+P24+Q24+R24+S24-T24+V24+W24+X24+Y24+Z24+U24</f>
         <v/>
@@ -9709,34 +10972,114 @@
           <t xml:space="preserve"> 4．其他</t>
         </is>
       </c>
-      <c r="B25" s="317" t="n"/>
-      <c r="C25" s="324" t="n"/>
+      <c r="B25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D25" s="324" t="n"/>
       <c r="E25" s="324" t="n"/>
-      <c r="F25" s="324" t="n"/>
-      <c r="G25" s="317" t="n"/>
-      <c r="H25" s="317" t="n"/>
-      <c r="I25" s="321" t="n"/>
-      <c r="J25" s="317" t="n"/>
-      <c r="K25" s="317" t="n"/>
-      <c r="L25" s="317" t="n"/>
-      <c r="M25" s="317" t="n"/>
+      <c r="F25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I25" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N25" s="318">
         <f>B25+C25+D25+E25+F25-G25+H25+I25+J25+K25+L25+M25</f>
         <v/>
       </c>
-      <c r="O25" s="324" t="n"/>
-      <c r="P25" s="324" t="n"/>
+      <c r="O25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q25" s="324" t="n"/>
       <c r="R25" s="324" t="n"/>
-      <c r="S25" s="324" t="n"/>
-      <c r="T25" s="321" t="n"/>
-      <c r="U25" s="317" t="n"/>
-      <c r="V25" s="317" t="n"/>
-      <c r="W25" s="324" t="n"/>
-      <c r="X25" s="317" t="n"/>
-      <c r="Y25" s="317" t="n"/>
-      <c r="Z25" s="317" t="n"/>
+      <c r="S25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T25" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA25" s="318">
         <f>O25+P25+Q25+R25+S25-T25+V25+W25+X25+Y25+Z25+U25</f>
         <v/>
@@ -9859,34 +11202,114 @@
           <t xml:space="preserve"> 1．资本公积转增股本（或资本）</t>
         </is>
       </c>
-      <c r="B27" s="317" t="n"/>
-      <c r="C27" s="324" t="n"/>
+      <c r="B27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D27" s="324" t="n"/>
       <c r="E27" s="324" t="n"/>
-      <c r="F27" s="324" t="n"/>
-      <c r="G27" s="317" t="n"/>
-      <c r="H27" s="317" t="n"/>
-      <c r="I27" s="321" t="n"/>
-      <c r="J27" s="317" t="n"/>
-      <c r="K27" s="317" t="n"/>
-      <c r="L27" s="317" t="n"/>
-      <c r="M27" s="317" t="n"/>
+      <c r="F27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I27" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N27" s="318">
         <f>B27+C27+D27+E27+F27-G27+H27+I27+J27+K27+L27+M27</f>
         <v/>
       </c>
-      <c r="O27" s="324" t="n"/>
-      <c r="P27" s="324" t="n"/>
+      <c r="O27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q27" s="324" t="n"/>
       <c r="R27" s="324" t="n"/>
-      <c r="S27" s="324" t="n"/>
-      <c r="T27" s="321" t="n"/>
-      <c r="U27" s="317" t="n"/>
-      <c r="V27" s="317" t="n"/>
-      <c r="W27" s="324" t="n"/>
-      <c r="X27" s="317" t="n"/>
-      <c r="Y27" s="317" t="n"/>
-      <c r="Z27" s="317" t="n"/>
+      <c r="S27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T27" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA27" s="318">
         <f>O27+P27+Q27+R27+S27-T27+V27+W27+X27+Y27+Z27+U27</f>
         <v/>
@@ -9898,34 +11321,114 @@
           <t xml:space="preserve"> 2．盈余公积转增股本（或资本）</t>
         </is>
       </c>
-      <c r="B28" s="317" t="n"/>
-      <c r="C28" s="324" t="n"/>
+      <c r="B28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D28" s="324" t="n"/>
       <c r="E28" s="324" t="n"/>
-      <c r="F28" s="324" t="n"/>
-      <c r="G28" s="317" t="n"/>
-      <c r="H28" s="317" t="n"/>
-      <c r="I28" s="321" t="n"/>
-      <c r="J28" s="317" t="n"/>
-      <c r="K28" s="317" t="n"/>
-      <c r="L28" s="317" t="n"/>
-      <c r="M28" s="317" t="n"/>
+      <c r="F28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I28" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N28" s="318">
         <f>B28+C28+D28+E28+F28-G28+H28+I28+J28+K28+L28+M28</f>
         <v/>
       </c>
-      <c r="O28" s="324" t="n"/>
-      <c r="P28" s="324" t="n"/>
+      <c r="O28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q28" s="324" t="n"/>
       <c r="R28" s="324" t="n"/>
-      <c r="S28" s="324" t="n"/>
-      <c r="T28" s="321" t="n"/>
-      <c r="U28" s="317" t="n"/>
-      <c r="V28" s="317" t="n"/>
-      <c r="W28" s="324" t="n"/>
-      <c r="X28" s="317" t="n"/>
-      <c r="Y28" s="317" t="n"/>
-      <c r="Z28" s="317" t="n"/>
+      <c r="S28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T28" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA28" s="318">
         <f>O28+P28+Q28+R28+S28-T28+V28+W28+X28+Y28+Z28+U28</f>
         <v/>
@@ -9937,34 +11440,114 @@
           <t xml:space="preserve"> 3．弥补亏损</t>
         </is>
       </c>
-      <c r="B29" s="317" t="n"/>
-      <c r="C29" s="324" t="n"/>
+      <c r="B29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D29" s="324" t="n"/>
       <c r="E29" s="324" t="n"/>
-      <c r="F29" s="324" t="n"/>
-      <c r="G29" s="317" t="n"/>
-      <c r="H29" s="317" t="n"/>
-      <c r="I29" s="321" t="n"/>
-      <c r="J29" s="317" t="n"/>
-      <c r="K29" s="317" t="n"/>
-      <c r="L29" s="317" t="n"/>
-      <c r="M29" s="317" t="n"/>
+      <c r="F29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I29" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N29" s="318">
         <f>B29+C29+D29+E29+F29-G29+H29+I29+J29+K29+L29+M29</f>
         <v/>
       </c>
-      <c r="O29" s="324" t="n"/>
-      <c r="P29" s="324" t="n"/>
+      <c r="O29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q29" s="324" t="n"/>
       <c r="R29" s="324" t="n"/>
-      <c r="S29" s="324" t="n"/>
-      <c r="T29" s="321" t="n"/>
-      <c r="U29" s="317" t="n"/>
-      <c r="V29" s="317" t="n"/>
-      <c r="W29" s="324" t="n"/>
-      <c r="X29" s="317" t="n"/>
-      <c r="Y29" s="317" t="n"/>
-      <c r="Z29" s="317" t="n"/>
+      <c r="S29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T29" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA29" s="318">
         <f>O29+P29+Q29+R29+S29-T29+V29+W29+X29+Y29+Z29+U29</f>
         <v/>
@@ -9976,34 +11559,114 @@
           <t xml:space="preserve"> 4.  设定受益计划变动额结转留存收益</t>
         </is>
       </c>
-      <c r="B30" s="317" t="n"/>
-      <c r="C30" s="324" t="n"/>
+      <c r="B30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D30" s="324" t="n"/>
       <c r="E30" s="324" t="n"/>
-      <c r="F30" s="324" t="n"/>
-      <c r="G30" s="317" t="n"/>
-      <c r="H30" s="317" t="n"/>
-      <c r="I30" s="321" t="n"/>
-      <c r="J30" s="317" t="n"/>
-      <c r="K30" s="317" t="n"/>
-      <c r="L30" s="317" t="n"/>
-      <c r="M30" s="317" t="n"/>
+      <c r="F30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I30" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N30" s="318">
         <f>B30+C30+D30+E30+F30-G30+H30+I30+J30+K30+L30+M30</f>
         <v/>
       </c>
-      <c r="O30" s="324" t="n"/>
-      <c r="P30" s="324" t="n"/>
+      <c r="O30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q30" s="324" t="n"/>
       <c r="R30" s="324" t="n"/>
-      <c r="S30" s="324" t="n"/>
-      <c r="T30" s="321" t="n"/>
-      <c r="U30" s="317" t="n"/>
-      <c r="V30" s="317" t="n"/>
-      <c r="W30" s="324" t="n"/>
-      <c r="X30" s="317" t="n"/>
-      <c r="Y30" s="317" t="n"/>
-      <c r="Z30" s="317" t="n"/>
+      <c r="S30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T30" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA30" s="318">
         <f>O30+P30+Q30+R30+S30-T30+V30+W30+X30+Y30+Z30+U30</f>
         <v/>
@@ -10015,32 +11678,120 @@
           <t xml:space="preserve"> 5．其他综合收益结转留存收益</t>
         </is>
       </c>
-      <c r="B31" s="317" t="n"/>
-      <c r="C31" s="324" t="n"/>
+      <c r="B31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C31" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D31" s="324" t="n"/>
       <c r="E31" s="324" t="n"/>
-      <c r="F31" s="324" t="n"/>
-      <c r="G31" s="317" t="n"/>
-      <c r="H31" s="317" t="n"/>
-      <c r="I31" s="321" t="n"/>
-      <c r="J31" s="317" t="n"/>
-      <c r="K31" s="317" t="n"/>
-      <c r="L31" s="317" t="n"/>
-      <c r="M31" s="317" t="n"/>
-      <c r="N31" s="318" t="n"/>
-      <c r="O31" s="324" t="n"/>
-      <c r="P31" s="324" t="n"/>
+      <c r="F31" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I31" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:minority_interest}}</t>
+        </is>
+      </c>
+      <c r="N31" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:total_equity}}</t>
+        </is>
+      </c>
+      <c r="O31" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P31" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q31" s="324" t="n"/>
       <c r="R31" s="324" t="n"/>
-      <c r="S31" s="324" t="n"/>
-      <c r="T31" s="321" t="n"/>
-      <c r="U31" s="317" t="n"/>
-      <c r="V31" s="317" t="n"/>
-      <c r="W31" s="324" t="n"/>
-      <c r="X31" s="317" t="n"/>
-      <c r="Y31" s="317" t="n"/>
-      <c r="Z31" s="317" t="n"/>
-      <c r="AA31" s="318" t="n"/>
+      <c r="S31" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T31" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W31" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z31" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:minority_interest}}</t>
+        </is>
+      </c>
+      <c r="AA31" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:total_equity}}</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="42" t="inlineStr">
@@ -10048,34 +11799,114 @@
           <t xml:space="preserve"> 6．其他</t>
         </is>
       </c>
-      <c r="B32" s="317" t="n"/>
-      <c r="C32" s="324" t="n"/>
+      <c r="B32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D32" s="324" t="n"/>
       <c r="E32" s="324" t="n"/>
-      <c r="F32" s="324" t="n"/>
-      <c r="G32" s="317" t="n"/>
-      <c r="H32" s="317" t="n"/>
-      <c r="I32" s="321" t="n"/>
-      <c r="J32" s="317" t="n"/>
-      <c r="K32" s="317" t="n"/>
-      <c r="L32" s="317" t="n"/>
-      <c r="M32" s="317" t="n"/>
+      <c r="F32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I32" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N32" s="318">
         <f>B32+C32+D32+E32+F32-G32+H32+I32+J32+K32+L32+M32</f>
         <v/>
       </c>
-      <c r="O32" s="324" t="n"/>
-      <c r="P32" s="324" t="n"/>
+      <c r="O32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q32" s="324" t="n"/>
       <c r="R32" s="324" t="n"/>
-      <c r="S32" s="324" t="n"/>
-      <c r="T32" s="321" t="n"/>
-      <c r="U32" s="317" t="n"/>
-      <c r="V32" s="317" t="n"/>
-      <c r="W32" s="324" t="n"/>
-      <c r="X32" s="317" t="n"/>
-      <c r="Y32" s="317" t="n"/>
-      <c r="Z32" s="317" t="n"/>
+      <c r="S32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T32" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA32" s="318">
         <f>O32+P32+Q32+R32+S32-T32+V32+W32+X32+Y32+Z32+U32</f>
         <v/>
@@ -10198,34 +12029,114 @@
           <t xml:space="preserve"> 1．本期提取</t>
         </is>
       </c>
-      <c r="B34" s="317" t="n"/>
-      <c r="C34" s="324" t="n"/>
+      <c r="B34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D34" s="324" t="n"/>
       <c r="E34" s="324" t="n"/>
-      <c r="F34" s="324" t="n"/>
-      <c r="G34" s="317" t="n"/>
-      <c r="H34" s="317" t="n"/>
-      <c r="I34" s="321" t="n"/>
-      <c r="J34" s="317" t="n"/>
-      <c r="K34" s="317" t="n"/>
-      <c r="L34" s="317" t="n"/>
-      <c r="M34" s="317" t="n"/>
+      <c r="F34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I34" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N34" s="318">
         <f>B34+C34+D34+E34+F34-G34+H34+I34+J34+K34+L34+M34</f>
         <v/>
       </c>
-      <c r="O34" s="324" t="n"/>
-      <c r="P34" s="324" t="n"/>
+      <c r="O34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q34" s="324" t="n"/>
       <c r="R34" s="324" t="n"/>
-      <c r="S34" s="324" t="n"/>
-      <c r="T34" s="321" t="n"/>
-      <c r="U34" s="317" t="n"/>
-      <c r="V34" s="317" t="n"/>
-      <c r="W34" s="324" t="n"/>
-      <c r="X34" s="317" t="n"/>
-      <c r="Y34" s="317" t="n"/>
-      <c r="Z34" s="317" t="n"/>
+      <c r="S34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T34" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA34" s="318">
         <f>O34+P34+Q34+R34+S34-T34+V34+W34+X34+Y34+Z34+U34</f>
         <v/>
@@ -10237,34 +12148,114 @@
           <t xml:space="preserve"> 2．本期使用（以负号填列）</t>
         </is>
       </c>
-      <c r="B35" s="317" t="n"/>
-      <c r="C35" s="324" t="n"/>
+      <c r="B35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C35" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D35" s="324" t="n"/>
       <c r="E35" s="324" t="n"/>
-      <c r="F35" s="324" t="n"/>
-      <c r="G35" s="317" t="n"/>
-      <c r="H35" s="317" t="n"/>
-      <c r="I35" s="321" t="n"/>
-      <c r="J35" s="317" t="n"/>
-      <c r="K35" s="317" t="n"/>
-      <c r="L35" s="317" t="n"/>
-      <c r="M35" s="317" t="n"/>
+      <c r="F35" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I35" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N35" s="318">
         <f>B35+C35+D35+E35+F35-G35+H35+I35+J35+K35+L35+M35</f>
         <v/>
       </c>
-      <c r="O35" s="324" t="n"/>
-      <c r="P35" s="324" t="n"/>
+      <c r="O35" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P35" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q35" s="324" t="n"/>
       <c r="R35" s="324" t="n"/>
-      <c r="S35" s="324" t="n"/>
-      <c r="T35" s="321" t="n"/>
-      <c r="U35" s="317" t="n"/>
-      <c r="V35" s="317" t="n"/>
-      <c r="W35" s="324" t="n"/>
-      <c r="X35" s="317" t="n"/>
-      <c r="Y35" s="317" t="n"/>
-      <c r="Z35" s="317" t="n"/>
+      <c r="S35" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T35" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W35" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z35" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA35" s="318">
         <f>O35+P35+Q35+R35+S35-T35+V35+W35+X35+Y35+Z35+U35</f>
         <v/>
@@ -10276,34 +12267,114 @@
           <t>（六）其他</t>
         </is>
       </c>
-      <c r="B36" s="317" t="n"/>
-      <c r="C36" s="324" t="n"/>
+      <c r="B36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C36" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="D36" s="324" t="n"/>
       <c r="E36" s="324" t="n"/>
-      <c r="F36" s="324" t="n"/>
-      <c r="G36" s="317" t="n"/>
-      <c r="H36" s="317" t="n"/>
-      <c r="I36" s="321" t="n"/>
-      <c r="J36" s="317" t="n"/>
-      <c r="K36" s="317" t="n"/>
-      <c r="L36" s="317" t="n"/>
-      <c r="M36" s="317" t="n"/>
+      <c r="F36" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I36" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="L36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="M36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="N36" s="318">
         <f>B36+C36+D36+E36+F36-G36+H36+I36+J36+K36+L36+M36</f>
         <v/>
       </c>
-      <c r="O36" s="324" t="n"/>
-      <c r="P36" s="324" t="n"/>
+      <c r="O36" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="P36" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
       <c r="Q36" s="324" t="n"/>
       <c r="R36" s="324" t="n"/>
-      <c r="S36" s="324" t="n"/>
-      <c r="T36" s="321" t="n"/>
-      <c r="U36" s="317" t="n"/>
-      <c r="V36" s="317" t="n"/>
-      <c r="W36" s="324" t="n"/>
-      <c r="X36" s="317" t="n"/>
-      <c r="Y36" s="317" t="n"/>
-      <c r="Z36" s="317" t="n"/>
+      <c r="S36" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="T36" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="U36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="V36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="W36" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="X36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:general_risk_reserve}}</t>
+        </is>
+      </c>
+      <c r="Y36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="Z36" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:minority_interest}}</t>
+        </is>
+      </c>
       <c r="AA36" s="318">
         <f>O36+P36+Q36+R36+S36-T36+V36+W36+X36+Y36+Z36+U36</f>
         <v/>
@@ -10454,6 +12525,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="331" t="inlineStr">
         <is>
@@ -10565,7 +12637,7 @@
       <c r="F2" s="7" t="n"/>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>2025年度</t>
+          <t>{{audit_year}}年度</t>
         </is>
       </c>
       <c r="H2" s="7" t="n"/>
@@ -10590,13 +12662,13 @@
     <row r="3" ht="21" customFormat="1" customHeight="1" s="58">
       <c r="A3" s="60" t="inlineStr">
         <is>
-          <t>编制单位：XXXX股份有限公司</t>
+          <t>编制单位：{{company_full_name}}</t>
         </is>
       </c>
       <c r="I3" s="9" t="n"/>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>单位：人民币元</t>
+          <t>单位：{{currency_unit}}</t>
         </is>
       </c>
       <c r="T3" s="9" t="n"/>
@@ -10797,30 +12869,102 @@
           <t>一、上年年末余额</t>
         </is>
       </c>
-      <c r="B7" s="317" t="n"/>
-      <c r="C7" s="324" t="n"/>
-      <c r="D7" s="324" t="n"/>
+      <c r="B7" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C7" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D7" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E7" s="324" t="n"/>
-      <c r="F7" s="324" t="n"/>
-      <c r="G7" s="317" t="n"/>
-      <c r="H7" s="320" t="n"/>
-      <c r="I7" s="324" t="n"/>
-      <c r="J7" s="317" t="n"/>
-      <c r="K7" s="317" t="n"/>
+      <c r="F7" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G7" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H7" s="320" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I7" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J7" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K7" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L7" s="335">
         <f>B7+C7+D7+E7+F7-G7+H7+I7+J7+K7</f>
         <v/>
       </c>
-      <c r="M7" s="324" t="n"/>
-      <c r="N7" s="318" t="n"/>
-      <c r="O7" s="320" t="n"/>
+      <c r="M7" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N7" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O7" s="320" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P7" s="320" t="n"/>
-      <c r="Q7" s="320" t="n"/>
-      <c r="R7" s="320" t="n"/>
-      <c r="S7" s="318" t="n"/>
-      <c r="T7" s="318" t="n"/>
-      <c r="U7" s="320" t="n"/>
-      <c r="V7" s="317" t="n"/>
+      <c r="Q7" s="320" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R7" s="320" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S7" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T7" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U7" s="320" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V7" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-001:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W7" s="318">
         <f>M7+N7+O7+P7+Q7-R7+S7+T7+U7+V7</f>
         <v/>
@@ -10832,30 +12976,102 @@
           <t xml:space="preserve">  加：会计政策变更</t>
         </is>
       </c>
-      <c r="B8" s="322" t="n"/>
-      <c r="C8" s="322" t="n"/>
-      <c r="D8" s="322" t="n"/>
+      <c r="B8" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C8" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D8" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E8" s="322" t="n"/>
-      <c r="F8" s="322" t="n"/>
-      <c r="G8" s="322" t="n"/>
-      <c r="H8" s="322" t="n"/>
-      <c r="I8" s="323" t="n"/>
-      <c r="J8" s="322" t="n"/>
-      <c r="K8" s="322" t="n"/>
+      <c r="F8" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G8" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H8" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I8" s="323" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J8" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K8" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L8" s="318">
         <f>B8+C8+D8+E8+F8-G8+H8+I8+J8+K8</f>
         <v/>
       </c>
-      <c r="M8" s="323" t="n"/>
-      <c r="N8" s="336" t="n"/>
-      <c r="O8" s="317" t="n"/>
+      <c r="M8" s="323" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N8" s="336" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O8" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P8" s="317" t="n"/>
-      <c r="Q8" s="317" t="n"/>
-      <c r="R8" s="317" t="n"/>
-      <c r="S8" s="318" t="n"/>
-      <c r="T8" s="318" t="n"/>
-      <c r="U8" s="317" t="n"/>
-      <c r="V8" s="317" t="n"/>
+      <c r="Q8" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R8" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S8" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T8" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U8" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V8" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-002:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W8" s="318">
         <f>M8+N8+O8+P8+Q8-R8+S8+T8+U8+V8</f>
         <v/>
@@ -10867,30 +13083,102 @@
           <t xml:space="preserve">           前期差错更正</t>
         </is>
       </c>
-      <c r="B9" s="322" t="n"/>
-      <c r="C9" s="322" t="n"/>
-      <c r="D9" s="322" t="n"/>
+      <c r="B9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E9" s="322" t="n"/>
-      <c r="F9" s="322" t="n"/>
-      <c r="G9" s="322" t="n"/>
-      <c r="H9" s="322" t="n"/>
-      <c r="I9" s="323" t="n"/>
-      <c r="J9" s="322" t="n"/>
-      <c r="K9" s="322" t="n"/>
+      <c r="F9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I9" s="323" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K9" s="322" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L9" s="318">
         <f>B9+C9+D9+E9+F9-G9+H9+I9+J9+K9</f>
         <v/>
       </c>
-      <c r="M9" s="323" t="n"/>
-      <c r="N9" s="336" t="n"/>
-      <c r="O9" s="317" t="n"/>
+      <c r="M9" s="323" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N9" s="336" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P9" s="317" t="n"/>
-      <c r="Q9" s="317" t="n"/>
-      <c r="R9" s="317" t="n"/>
-      <c r="S9" s="318" t="n"/>
-      <c r="T9" s="318" t="n"/>
-      <c r="U9" s="317" t="n"/>
-      <c r="V9" s="317" t="n"/>
+      <c r="Q9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S9" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T9" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V9" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-003:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W9" s="318">
         <f>M9+N9+O9+P9+Q9-R9+S9+T9+U9+V9</f>
         <v/>
@@ -10902,30 +13190,102 @@
           <t xml:space="preserve">           其他</t>
         </is>
       </c>
-      <c r="B10" s="317" t="n"/>
-      <c r="C10" s="324" t="n"/>
-      <c r="D10" s="324" t="n"/>
+      <c r="B10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C10" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D10" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E10" s="324" t="n"/>
-      <c r="F10" s="324" t="n"/>
-      <c r="G10" s="317" t="n"/>
-      <c r="H10" s="317" t="n"/>
-      <c r="I10" s="321" t="n"/>
-      <c r="J10" s="317" t="n"/>
-      <c r="K10" s="317" t="n"/>
+      <c r="F10" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I10" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L10" s="318">
         <f>B10+C10+D10+E10+F10-G10+H10+I10+J10+K10</f>
         <v/>
       </c>
-      <c r="M10" s="324" t="n"/>
-      <c r="N10" s="318" t="n"/>
-      <c r="O10" s="317" t="n"/>
+      <c r="M10" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N10" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P10" s="317" t="n"/>
-      <c r="Q10" s="317" t="n"/>
-      <c r="R10" s="317" t="n"/>
-      <c r="S10" s="318" t="n"/>
-      <c r="T10" s="318" t="n"/>
-      <c r="U10" s="317" t="n"/>
-      <c r="V10" s="317" t="n"/>
+      <c r="Q10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S10" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T10" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V10" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-005:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W10" s="318">
         <f>M10+N10+O10+P10+Q10-R10+S10+T10+U10+V10</f>
         <v/>
@@ -11127,30 +13487,102 @@
           <t>（一）综合收益总额</t>
         </is>
       </c>
-      <c r="B13" s="317" t="n"/>
-      <c r="C13" s="317" t="n"/>
-      <c r="D13" s="317" t="n"/>
+      <c r="B13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E13" s="317" t="n"/>
-      <c r="F13" s="317" t="n"/>
-      <c r="G13" s="317" t="n"/>
-      <c r="H13" s="317" t="n"/>
-      <c r="I13" s="324" t="n"/>
-      <c r="J13" s="317" t="n"/>
-      <c r="K13" s="317" t="n"/>
+      <c r="F13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I13" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L13" s="318">
         <f>B13+C13+D13+E13+F13-G13+H13+I13+J13+K13</f>
         <v/>
       </c>
-      <c r="M13" s="324" t="n"/>
-      <c r="N13" s="317" t="n"/>
-      <c r="O13" s="324" t="n"/>
+      <c r="M13" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O13" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P13" s="324" t="n"/>
-      <c r="Q13" s="324" t="n"/>
-      <c r="R13" s="324" t="n"/>
-      <c r="S13" s="317" t="n"/>
-      <c r="T13" s="318" t="n"/>
-      <c r="U13" s="317" t="n"/>
-      <c r="V13" s="317" t="n"/>
+      <c r="Q13" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R13" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T13" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V13" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-008:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W13" s="318">
         <f>M13+N13+O13+P13+Q13-R13+S13+T13+U13+V13</f>
         <v/>
@@ -11257,30 +13689,102 @@
           <t xml:space="preserve"> 1．股东投入的普通股</t>
         </is>
       </c>
-      <c r="B15" s="317" t="n"/>
-      <c r="C15" s="324" t="n"/>
-      <c r="D15" s="324" t="n"/>
+      <c r="B15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E15" s="324" t="n"/>
-      <c r="F15" s="324" t="n"/>
-      <c r="G15" s="317" t="n"/>
-      <c r="H15" s="317" t="n"/>
-      <c r="I15" s="321" t="n"/>
-      <c r="J15" s="317" t="n"/>
-      <c r="K15" s="317" t="n"/>
+      <c r="F15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I15" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L15" s="318">
         <f>B15+C15+D15+E15+F15-G15+H15+I15+J15+K15</f>
         <v/>
       </c>
-      <c r="M15" s="324" t="n"/>
-      <c r="N15" s="317" t="n"/>
-      <c r="O15" s="324" t="n"/>
+      <c r="M15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P15" s="324" t="n"/>
-      <c r="Q15" s="324" t="n"/>
-      <c r="R15" s="324" t="n"/>
-      <c r="S15" s="324" t="n"/>
-      <c r="T15" s="321" t="n"/>
-      <c r="U15" s="317" t="n"/>
-      <c r="V15" s="317" t="n"/>
+      <c r="Q15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S15" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T15" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V15" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-010:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W15" s="318">
         <f>M15+N15+O15+P15+Q15-R15+S15+T15+U15+V15</f>
         <v/>
@@ -11292,30 +13796,102 @@
           <t xml:space="preserve"> 2.  其他权益工具持有者投入资本</t>
         </is>
       </c>
-      <c r="B16" s="317" t="n"/>
-      <c r="C16" s="324" t="n"/>
-      <c r="D16" s="324" t="n"/>
+      <c r="B16" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C16" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D16" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E16" s="324" t="n"/>
-      <c r="F16" s="324" t="n"/>
-      <c r="G16" s="317" t="n"/>
-      <c r="H16" s="317" t="n"/>
-      <c r="I16" s="321" t="n"/>
-      <c r="J16" s="317" t="n"/>
-      <c r="K16" s="317" t="n"/>
+      <c r="F16" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G16" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H16" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I16" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J16" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K16" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L16" s="318">
         <f>B16+C16+D16+E16+F16-G16+H16+I16+J16+K16</f>
         <v/>
       </c>
-      <c r="M16" s="324" t="n"/>
-      <c r="N16" s="317" t="n"/>
-      <c r="O16" s="324" t="n"/>
+      <c r="M16" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N16" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O16" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P16" s="324" t="n"/>
-      <c r="Q16" s="324" t="n"/>
-      <c r="R16" s="324" t="n"/>
-      <c r="S16" s="324" t="n"/>
-      <c r="T16" s="321" t="n"/>
-      <c r="U16" s="317" t="n"/>
-      <c r="V16" s="317" t="n"/>
+      <c r="Q16" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R16" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S16" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T16" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U16" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V16" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-011:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W16" s="318">
         <f>M16+N16+O16+P16+Q16-R16+S16+T16+U16+V16</f>
         <v/>
@@ -11327,30 +13903,102 @@
           <t xml:space="preserve"> 3．股份支付计入股东权益的金额</t>
         </is>
       </c>
-      <c r="B17" s="317" t="n"/>
-      <c r="C17" s="324" t="n"/>
-      <c r="D17" s="324" t="n"/>
+      <c r="B17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E17" s="324" t="n"/>
-      <c r="F17" s="324" t="n"/>
-      <c r="G17" s="317" t="n"/>
-      <c r="H17" s="317" t="n"/>
-      <c r="I17" s="321" t="n"/>
-      <c r="J17" s="317" t="n"/>
-      <c r="K17" s="317" t="n"/>
+      <c r="F17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I17" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L17" s="318">
         <f>B17+C17+D17+E17+F17-G17+H17+I17+J17+K17</f>
         <v/>
       </c>
-      <c r="M17" s="324" t="n"/>
-      <c r="N17" s="317" t="n"/>
-      <c r="O17" s="324" t="n"/>
+      <c r="M17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P17" s="324" t="n"/>
-      <c r="Q17" s="324" t="n"/>
-      <c r="R17" s="324" t="n"/>
-      <c r="S17" s="324" t="n"/>
-      <c r="T17" s="321" t="n"/>
-      <c r="U17" s="317" t="n"/>
-      <c r="V17" s="317" t="n"/>
+      <c r="Q17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S17" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T17" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V17" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-012:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W17" s="318">
         <f>M17+N17+O17+P17+Q17-R17+S17+T17+U17+V17</f>
         <v/>
@@ -11362,30 +14010,102 @@
           <t xml:space="preserve"> 4．其他</t>
         </is>
       </c>
-      <c r="B18" s="317" t="n"/>
-      <c r="C18" s="324" t="n"/>
-      <c r="D18" s="324" t="n"/>
+      <c r="B18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E18" s="324" t="n"/>
-      <c r="F18" s="324" t="n"/>
-      <c r="G18" s="317" t="n"/>
-      <c r="H18" s="317" t="n"/>
-      <c r="I18" s="321" t="n"/>
-      <c r="J18" s="317" t="n"/>
-      <c r="K18" s="317" t="n"/>
+      <c r="F18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I18" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L18" s="318">
         <f>B18+C18+D18+E18+F18-G18+H18+I18+J18+K18</f>
         <v/>
       </c>
-      <c r="M18" s="324" t="n"/>
-      <c r="N18" s="317" t="n"/>
-      <c r="O18" s="324" t="n"/>
+      <c r="M18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P18" s="324" t="n"/>
-      <c r="Q18" s="324" t="n"/>
-      <c r="R18" s="324" t="n"/>
-      <c r="S18" s="324" t="n"/>
-      <c r="T18" s="321" t="n"/>
-      <c r="U18" s="317" t="n"/>
-      <c r="V18" s="317" t="n"/>
+      <c r="Q18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S18" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T18" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V18" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W18" s="318">
         <f>M18+N18+O18+P18+Q18-R18+S18+T18+U18+V18</f>
         <v/>
@@ -11492,30 +14212,102 @@
           <t xml:space="preserve"> 1．提取盈余公积</t>
         </is>
       </c>
-      <c r="B20" s="317" t="n"/>
-      <c r="C20" s="324" t="n"/>
-      <c r="D20" s="324" t="n"/>
+      <c r="B20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E20" s="324" t="n"/>
-      <c r="F20" s="324" t="n"/>
-      <c r="G20" s="317" t="n"/>
-      <c r="H20" s="317" t="n"/>
-      <c r="I20" s="321" t="n"/>
-      <c r="J20" s="317" t="n"/>
-      <c r="K20" s="317" t="n"/>
+      <c r="F20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I20" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L20" s="318">
         <f>B20+C20+D20+E20+F20-G20+H20+I20+J20+K20</f>
         <v/>
       </c>
-      <c r="M20" s="324" t="n"/>
-      <c r="N20" s="317" t="n"/>
-      <c r="O20" s="324" t="n"/>
+      <c r="M20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P20" s="324" t="n"/>
-      <c r="Q20" s="324" t="n"/>
-      <c r="R20" s="324" t="n"/>
-      <c r="S20" s="324" t="n"/>
-      <c r="T20" s="321" t="n"/>
-      <c r="U20" s="317" t="n"/>
-      <c r="V20" s="317" t="n"/>
+      <c r="Q20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S20" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T20" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V20" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-015:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W20" s="318">
         <f>M20+N20+O20+P20+Q20-R20+S20+T20+U20+V20</f>
         <v/>
@@ -11527,28 +14319,108 @@
           <t xml:space="preserve"> 2．提取一般风险准备</t>
         </is>
       </c>
-      <c r="B21" s="317" t="n"/>
-      <c r="C21" s="324" t="n"/>
-      <c r="D21" s="324" t="n"/>
+      <c r="B21" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C21" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D21" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E21" s="324" t="n"/>
-      <c r="F21" s="324" t="n"/>
-      <c r="G21" s="317" t="n"/>
-      <c r="H21" s="317" t="n"/>
-      <c r="I21" s="321" t="n"/>
-      <c r="J21" s="317" t="n"/>
-      <c r="K21" s="317" t="n"/>
-      <c r="L21" s="318" t="n"/>
-      <c r="M21" s="324" t="n"/>
-      <c r="N21" s="317" t="n"/>
-      <c r="O21" s="324" t="n"/>
+      <c r="F21" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G21" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H21" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I21" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J21" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K21" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="L21" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:current_year:total_equity}}</t>
+        </is>
+      </c>
+      <c r="M21" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N21" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O21" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P21" s="324" t="n"/>
-      <c r="Q21" s="324" t="n"/>
-      <c r="R21" s="324" t="n"/>
-      <c r="S21" s="324" t="n"/>
-      <c r="T21" s="321" t="n"/>
-      <c r="U21" s="317" t="n"/>
-      <c r="V21" s="317" t="n"/>
-      <c r="W21" s="318" t="n"/>
+      <c r="Q21" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R21" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S21" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T21" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U21" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V21" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="W21" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-016:prior_year:total_equity}}</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customFormat="1" customHeight="1" s="58">
       <c r="A22" s="42" t="inlineStr">
@@ -11556,30 +14428,102 @@
           <t xml:space="preserve"> 3．对股东（或所有者）的分配</t>
         </is>
       </c>
-      <c r="B22" s="317" t="n"/>
-      <c r="C22" s="324" t="n"/>
-      <c r="D22" s="324" t="n"/>
+      <c r="B22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E22" s="324" t="n"/>
-      <c r="F22" s="324" t="n"/>
-      <c r="G22" s="317" t="n"/>
-      <c r="H22" s="317" t="n"/>
-      <c r="I22" s="321" t="n"/>
-      <c r="J22" s="317" t="n"/>
-      <c r="K22" s="317" t="n"/>
+      <c r="F22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I22" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L22" s="318">
         <f>B22+C22+D22+E22+F22-G22+H22+I22+J22+K22</f>
         <v/>
       </c>
-      <c r="M22" s="324" t="n"/>
-      <c r="N22" s="317" t="n"/>
-      <c r="O22" s="324" t="n"/>
+      <c r="M22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P22" s="324" t="n"/>
-      <c r="Q22" s="324" t="n"/>
-      <c r="R22" s="324" t="n"/>
-      <c r="S22" s="324" t="n"/>
-      <c r="T22" s="321" t="n"/>
-      <c r="U22" s="317" t="n"/>
-      <c r="V22" s="317" t="n"/>
+      <c r="Q22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S22" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T22" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V22" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-017:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W22" s="318">
         <f>M22+N22+O22+P22+Q22-R22+S22+T22+U22+V22</f>
         <v/>
@@ -11591,30 +14535,102 @@
           <t xml:space="preserve"> 4．其他</t>
         </is>
       </c>
-      <c r="B23" s="317" t="n"/>
-      <c r="C23" s="324" t="n"/>
-      <c r="D23" s="324" t="n"/>
+      <c r="B23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E23" s="324" t="n"/>
-      <c r="F23" s="324" t="n"/>
-      <c r="G23" s="317" t="n"/>
-      <c r="H23" s="317" t="n"/>
-      <c r="I23" s="321" t="n"/>
-      <c r="J23" s="317" t="n"/>
-      <c r="K23" s="317" t="n"/>
+      <c r="F23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I23" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L23" s="318">
         <f>B23+C23+D23+E23+F23-G23+H23+I23+J23+K23</f>
         <v/>
       </c>
-      <c r="M23" s="324" t="n"/>
-      <c r="N23" s="317" t="n"/>
-      <c r="O23" s="324" t="n"/>
+      <c r="M23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P23" s="324" t="n"/>
-      <c r="Q23" s="324" t="n"/>
-      <c r="R23" s="324" t="n"/>
-      <c r="S23" s="324" t="n"/>
-      <c r="T23" s="321" t="n"/>
-      <c r="U23" s="317" t="n"/>
-      <c r="V23" s="317" t="n"/>
+      <c r="Q23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S23" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T23" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V23" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-013:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W23" s="318">
         <f>M23+N23+O23+P23+Q23-R23+S23+T23+U23+V23</f>
         <v/>
@@ -11721,30 +14737,102 @@
           <t xml:space="preserve"> 1．资本公积转增股本（或资本）</t>
         </is>
       </c>
-      <c r="B25" s="317" t="n"/>
-      <c r="C25" s="324" t="n"/>
-      <c r="D25" s="324" t="n"/>
+      <c r="B25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E25" s="324" t="n"/>
-      <c r="F25" s="324" t="n"/>
-      <c r="G25" s="317" t="n"/>
-      <c r="H25" s="317" t="n"/>
-      <c r="I25" s="321" t="n"/>
-      <c r="J25" s="317" t="n"/>
-      <c r="K25" s="317" t="n"/>
+      <c r="F25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I25" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L25" s="318">
         <f>B25+C25+D25+E25+F25-G25+H25+I25+J25+K25</f>
         <v/>
       </c>
-      <c r="M25" s="324" t="n"/>
-      <c r="N25" s="317" t="n"/>
-      <c r="O25" s="324" t="n"/>
+      <c r="M25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P25" s="324" t="n"/>
-      <c r="Q25" s="324" t="n"/>
-      <c r="R25" s="324" t="n"/>
-      <c r="S25" s="324" t="n"/>
-      <c r="T25" s="321" t="n"/>
-      <c r="U25" s="317" t="n"/>
-      <c r="V25" s="317" t="n"/>
+      <c r="Q25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S25" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T25" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V25" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-020:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W25" s="318">
         <f>M25+N25+O25+P25+Q25-R25+S25+T25+U25+V25</f>
         <v/>
@@ -11756,30 +14844,102 @@
           <t xml:space="preserve"> 2．盈余公积转增股本（或资本）</t>
         </is>
       </c>
-      <c r="B26" s="317" t="n"/>
-      <c r="C26" s="324" t="n"/>
-      <c r="D26" s="324" t="n"/>
+      <c r="B26" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C26" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D26" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E26" s="324" t="n"/>
-      <c r="F26" s="324" t="n"/>
-      <c r="G26" s="317" t="n"/>
-      <c r="H26" s="317" t="n"/>
-      <c r="I26" s="321" t="n"/>
-      <c r="J26" s="317" t="n"/>
-      <c r="K26" s="317" t="n"/>
+      <c r="F26" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G26" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H26" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I26" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J26" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K26" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L26" s="318">
         <f>B26+C26+D26+E26+F26-G26+H26+I26+J26+K26</f>
         <v/>
       </c>
-      <c r="M26" s="324" t="n"/>
-      <c r="N26" s="317" t="n"/>
-      <c r="O26" s="324" t="n"/>
+      <c r="M26" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N26" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O26" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P26" s="324" t="n"/>
-      <c r="Q26" s="324" t="n"/>
-      <c r="R26" s="324" t="n"/>
-      <c r="S26" s="324" t="n"/>
-      <c r="T26" s="321" t="n"/>
-      <c r="U26" s="317" t="n"/>
-      <c r="V26" s="317" t="n"/>
+      <c r="Q26" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R26" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S26" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T26" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U26" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V26" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-021:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W26" s="318">
         <f>M26+N26+O26+P26+Q26-R26+S26+T26+U26+V26</f>
         <v/>
@@ -11791,30 +14951,102 @@
           <t xml:space="preserve"> 3．弥补亏损</t>
         </is>
       </c>
-      <c r="B27" s="317" t="n"/>
-      <c r="C27" s="324" t="n"/>
-      <c r="D27" s="324" t="n"/>
+      <c r="B27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E27" s="324" t="n"/>
-      <c r="F27" s="324" t="n"/>
-      <c r="G27" s="317" t="n"/>
-      <c r="H27" s="317" t="n"/>
-      <c r="I27" s="321" t="n"/>
-      <c r="J27" s="317" t="n"/>
-      <c r="K27" s="317" t="n"/>
+      <c r="F27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I27" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L27" s="318">
         <f>B27+C27+D27+E27+F27-G27+H27+I27+J27+K27</f>
         <v/>
       </c>
-      <c r="M27" s="324" t="n"/>
-      <c r="N27" s="317" t="n"/>
-      <c r="O27" s="324" t="n"/>
+      <c r="M27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P27" s="324" t="n"/>
-      <c r="Q27" s="324" t="n"/>
-      <c r="R27" s="324" t="n"/>
-      <c r="S27" s="324" t="n"/>
-      <c r="T27" s="321" t="n"/>
-      <c r="U27" s="317" t="n"/>
-      <c r="V27" s="317" t="n"/>
+      <c r="Q27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S27" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T27" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V27" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-022:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W27" s="318">
         <f>M27+N27+O27+P27+Q27-R27+S27+T27+U27+V27</f>
         <v/>
@@ -11826,30 +15058,102 @@
           <t xml:space="preserve"> 4.  设定受益计划变动额结转留存收益</t>
         </is>
       </c>
-      <c r="B28" s="317" t="n"/>
-      <c r="C28" s="324" t="n"/>
-      <c r="D28" s="324" t="n"/>
+      <c r="B28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E28" s="324" t="n"/>
-      <c r="F28" s="324" t="n"/>
-      <c r="G28" s="317" t="n"/>
-      <c r="H28" s="317" t="n"/>
-      <c r="I28" s="321" t="n"/>
-      <c r="J28" s="317" t="n"/>
-      <c r="K28" s="317" t="n"/>
+      <c r="F28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I28" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L28" s="318">
         <f>B28+C28+D28+E28+F28-G28+H28+I28+J28+K28</f>
         <v/>
       </c>
-      <c r="M28" s="324" t="n"/>
-      <c r="N28" s="317" t="n"/>
-      <c r="O28" s="324" t="n"/>
+      <c r="M28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P28" s="324" t="n"/>
-      <c r="Q28" s="324" t="n"/>
-      <c r="R28" s="324" t="n"/>
-      <c r="S28" s="324" t="n"/>
-      <c r="T28" s="321" t="n"/>
-      <c r="U28" s="317" t="n"/>
-      <c r="V28" s="317" t="n"/>
+      <c r="Q28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S28" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T28" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V28" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-023:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W28" s="318">
         <f>M28+N28+O28+P28+Q28-R28+S28+T28+U28+V28</f>
         <v/>
@@ -11861,28 +15165,108 @@
           <t xml:space="preserve"> 5．其他综合收益结转留存收益</t>
         </is>
       </c>
-      <c r="B29" s="317" t="n"/>
-      <c r="C29" s="324" t="n"/>
-      <c r="D29" s="324" t="n"/>
+      <c r="B29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E29" s="324" t="n"/>
-      <c r="F29" s="324" t="n"/>
-      <c r="G29" s="317" t="n"/>
-      <c r="H29" s="317" t="n"/>
-      <c r="I29" s="321" t="n"/>
-      <c r="J29" s="317" t="n"/>
-      <c r="K29" s="317" t="n"/>
-      <c r="L29" s="318" t="n"/>
-      <c r="M29" s="324" t="n"/>
-      <c r="N29" s="317" t="n"/>
-      <c r="O29" s="324" t="n"/>
+      <c r="F29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I29" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="L29" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:current_year:total_equity}}</t>
+        </is>
+      </c>
+      <c r="M29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P29" s="324" t="n"/>
-      <c r="Q29" s="324" t="n"/>
-      <c r="R29" s="324" t="n"/>
-      <c r="S29" s="324" t="n"/>
-      <c r="T29" s="321" t="n"/>
-      <c r="U29" s="317" t="n"/>
-      <c r="V29" s="317" t="n"/>
-      <c r="W29" s="318" t="n"/>
+      <c r="Q29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S29" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T29" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V29" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
+      <c r="W29" s="318" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-024:prior_year:total_equity}}</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customFormat="1" customHeight="1" s="58">
       <c r="A30" s="42" t="inlineStr">
@@ -11890,30 +15274,102 @@
           <t xml:space="preserve"> 6．其他</t>
         </is>
       </c>
-      <c r="B30" s="317" t="n"/>
-      <c r="C30" s="324" t="n"/>
-      <c r="D30" s="324" t="n"/>
+      <c r="B30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E30" s="324" t="n"/>
-      <c r="F30" s="324" t="n"/>
-      <c r="G30" s="317" t="n"/>
-      <c r="H30" s="317" t="n"/>
-      <c r="I30" s="321" t="n"/>
-      <c r="J30" s="317" t="n"/>
-      <c r="K30" s="317" t="n"/>
+      <c r="F30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I30" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L30" s="318">
         <f>B30+C30+D30+E30+F30-G30+H30+I30+J30+K30</f>
         <v/>
       </c>
-      <c r="M30" s="324" t="n"/>
-      <c r="N30" s="317" t="n"/>
-      <c r="O30" s="324" t="n"/>
+      <c r="M30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P30" s="324" t="n"/>
-      <c r="Q30" s="324" t="n"/>
-      <c r="R30" s="324" t="n"/>
-      <c r="S30" s="324" t="n"/>
-      <c r="T30" s="321" t="n"/>
-      <c r="U30" s="317" t="n"/>
-      <c r="V30" s="317" t="n"/>
+      <c r="Q30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S30" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T30" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V30" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-025:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W30" s="318">
         <f>M30+N30+O30+P30+Q30-R30+S30+T30+U30+V30</f>
         <v/>
@@ -12020,30 +15476,102 @@
           <t xml:space="preserve"> 1．本期提取</t>
         </is>
       </c>
-      <c r="B32" s="317" t="n"/>
-      <c r="C32" s="324" t="n"/>
-      <c r="D32" s="324" t="n"/>
+      <c r="B32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E32" s="324" t="n"/>
-      <c r="F32" s="324" t="n"/>
-      <c r="G32" s="317" t="n"/>
-      <c r="H32" s="317" t="n"/>
-      <c r="I32" s="321" t="n"/>
-      <c r="J32" s="317" t="n"/>
-      <c r="K32" s="317" t="n"/>
+      <c r="F32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I32" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L32" s="318">
         <f>B32+C32+D32+E32+F32-G32+H32+I32+J32+K32</f>
         <v/>
       </c>
-      <c r="M32" s="324" t="n"/>
-      <c r="N32" s="317" t="n"/>
-      <c r="O32" s="324" t="n"/>
+      <c r="M32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P32" s="324" t="n"/>
-      <c r="Q32" s="324" t="n"/>
-      <c r="R32" s="324" t="n"/>
-      <c r="S32" s="324" t="n"/>
-      <c r="T32" s="321" t="n"/>
-      <c r="U32" s="317" t="n"/>
-      <c r="V32" s="317" t="n"/>
+      <c r="Q32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S32" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T32" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V32" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-027:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W32" s="318">
         <f>M32+N32+O32+P32+Q32-R32+S32+T32+U32+V32</f>
         <v/>
@@ -12055,30 +15583,102 @@
           <t xml:space="preserve"> 2．本期使用（以负号填列）</t>
         </is>
       </c>
-      <c r="B33" s="317" t="n"/>
-      <c r="C33" s="324" t="n"/>
-      <c r="D33" s="324" t="n"/>
+      <c r="B33" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C33" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D33" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E33" s="324" t="n"/>
-      <c r="F33" s="324" t="n"/>
-      <c r="G33" s="317" t="n"/>
-      <c r="H33" s="317" t="n"/>
-      <c r="I33" s="321" t="n"/>
-      <c r="J33" s="317" t="n"/>
-      <c r="K33" s="317" t="n"/>
+      <c r="F33" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G33" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H33" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I33" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J33" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K33" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L33" s="318">
         <f>B33+C33+D33+E33+F33-G33+H33+I33+J33+K33</f>
         <v/>
       </c>
-      <c r="M33" s="324" t="n"/>
-      <c r="N33" s="317" t="n"/>
-      <c r="O33" s="324" t="n"/>
+      <c r="M33" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N33" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O33" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P33" s="324" t="n"/>
-      <c r="Q33" s="324" t="n"/>
-      <c r="R33" s="324" t="n"/>
-      <c r="S33" s="324" t="n"/>
-      <c r="T33" s="321" t="n"/>
-      <c r="U33" s="317" t="n"/>
-      <c r="V33" s="317" t="n"/>
+      <c r="Q33" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R33" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S33" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T33" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U33" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V33" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-028:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W33" s="318">
         <f>M33+N33+O33+P33+Q33-R33+S33+T33+U33+V33</f>
         <v/>
@@ -12090,30 +15690,102 @@
           <t>（六）其他</t>
         </is>
       </c>
-      <c r="B34" s="317" t="n"/>
-      <c r="C34" s="324" t="n"/>
-      <c r="D34" s="324" t="n"/>
+      <c r="B34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="C34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="D34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="E34" s="324" t="n"/>
-      <c r="F34" s="324" t="n"/>
-      <c r="G34" s="317" t="n"/>
-      <c r="H34" s="317" t="n"/>
-      <c r="I34" s="321" t="n"/>
-      <c r="J34" s="317" t="n"/>
-      <c r="K34" s="317" t="n"/>
+      <c r="F34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="G34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="H34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="I34" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="J34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="K34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:current_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="L34" s="318">
         <f>B34+C34+D34+E34+F34-G34+H34+I34+J34+K34</f>
         <v/>
       </c>
-      <c r="M34" s="324" t="n"/>
-      <c r="N34" s="317" t="n"/>
-      <c r="O34" s="324" t="n"/>
+      <c r="M34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:share_capital}}</t>
+        </is>
+      </c>
+      <c r="N34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:other_equity_instrument}}</t>
+        </is>
+      </c>
+      <c r="O34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:perpetual_bond}}</t>
+        </is>
+      </c>
       <c r="P34" s="324" t="n"/>
-      <c r="Q34" s="324" t="n"/>
-      <c r="R34" s="324" t="n"/>
-      <c r="S34" s="324" t="n"/>
-      <c r="T34" s="321" t="n"/>
-      <c r="U34" s="317" t="n"/>
-      <c r="V34" s="317" t="n"/>
+      <c r="Q34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:capital_reserve}}</t>
+        </is>
+      </c>
+      <c r="R34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:treasury_stock}}</t>
+        </is>
+      </c>
+      <c r="S34" s="324" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:other_comprehensive_income}}</t>
+        </is>
+      </c>
+      <c r="T34" s="321" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:special_reserve}}</t>
+        </is>
+      </c>
+      <c r="U34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:surplus_reserve}}</t>
+        </is>
+      </c>
+      <c r="V34" s="317" t="inlineStr">
+        <is>
+          <t>{{eq:EQ-029:prior_year:retained_earnings}}</t>
+        </is>
+      </c>
       <c r="W34" s="318">
         <f>M34+N34+O34+P34+Q34-R34+S34+T34+U34+V34</f>
         <v/>
